--- a/大学物理实验/实验九 旋光性溶液浓度的测量/实验九 旋光性溶液浓度的测量.xlsx
+++ b/大学物理实验/实验九 旋光性溶液浓度的测量/实验九 旋光性溶液浓度的测量.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GDUT-REVIEW-NOTES\大学物理实验\实验九 旋光性溶液浓度的测量\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BA85E85-CC8B-4761-9AD2-BF5EA89FAC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEB2DCD-0D3A-4863-9F23-1D1B20D88B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3E91FE0B-0291-4E21-BA97-2D30C83FC55D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3E91FE0B-0291-4E21-BA97-2D30C83FC55D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -83,14 +81,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>温度t = 23.2 ℃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>试管长l = 20cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>表9-1 旋光角测量数据记录表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,6 +106,14 @@
   </si>
   <si>
     <t>B=</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温度t = 26.3 ℃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>试管长l = 20.0cm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -204,24 +202,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -240,6 +223,18 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -348,8 +343,8 @@
           <c:h val="0.6645343646700681"/>
         </c:manualLayout>
       </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -358,16 +353,26 @@
             <c:v>旋光角</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:trendline>
             <c:spPr>
@@ -375,15 +380,45 @@
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:prstDash val="sysDot"/>
+                <a:prstDash val="solid"/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
-          <c:cat>
+          <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$A$7:$A$11</c:f>
               <c:numCache>
@@ -406,31 +441,31 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Sheet1!$M$7:$M$11</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.9550000000000005</c:v>
+                  <c:v>2.665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.42</c:v>
+                  <c:v>5.7099999999999991</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.2149999999999999</c:v>
+                  <c:v>8.0399999999999991</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.190000000000001</c:v>
+                  <c:v>10.824999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.355</c:v>
+                  <c:v>13.694999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -446,11 +481,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
         <c:axId val="1814178032"/>
         <c:axId val="1814174672"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="1814178032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -487,8 +521,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.40954867328384903"/>
-              <c:y val="0.91532533740145516"/>
+              <c:x val="0.11416048463276944"/>
+              <c:y val="0.9109577923194484"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -559,11 +593,8 @@
         </c:txPr>
         <c:crossAx val="1814174672"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="1814174672"/>
         <c:scaling>
@@ -673,7 +704,7 @@
         </c:txPr>
         <c:crossAx val="1814178032"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1380,8 +1411,8 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="812081" cy="177228"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="文本框 2">
@@ -1423,6 +1454,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1500,7 +1532,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="文本框 2">
@@ -1564,8 +1596,8 @@
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="364139" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="文本框 3">
@@ -1607,6 +1639,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1665,7 +1698,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="文本框 3">
@@ -1729,8 +1762,8 @@
       <xdr:rowOff>174381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>73269</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>545123</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>92808</xdr:rowOff>
     </xdr:to>
@@ -1760,9 +1793,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>677920</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>104105</xdr:rowOff>
+      <xdr:colOff>525521</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>16182</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="173766" cy="364139"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1780,7 +1813,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm rot="16200000">
-              <a:off x="582733" y="3437792"/>
+              <a:off x="430334" y="3516923"/>
               <a:ext cx="364139" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1808,6 +1841,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -1880,7 +1914,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm rot="16200000">
-              <a:off x="582733" y="3437792"/>
+              <a:off x="430334" y="3516923"/>
               <a:ext cx="364139" cy="173766"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1908,6 +1942,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -1924,10 +1959,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>650141</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>547564</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>31749</xdr:rowOff>
+      <xdr:rowOff>8303</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="812081" cy="177228"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -1945,7 +1980,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3224333" y="5204557"/>
+              <a:off x="1672979" y="5172318"/>
               <a:ext cx="812081" cy="177228"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1973,6 +2008,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2064,7 +2100,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3224333" y="5204557"/>
+              <a:off x="1672979" y="5172318"/>
               <a:ext cx="812081" cy="177228"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2092,6 +2128,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2169,8 +2206,8 @@
       <xdr:rowOff>116743</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="362407" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="文本框 9">
@@ -2212,6 +2249,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -2256,7 +2294,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="文本框 9">
@@ -2315,15 +2353,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>200270</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>73269</xdr:rowOff>
+      <xdr:rowOff>96715</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>210039</xdr:colOff>
+      <xdr:colOff>157285</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>19538</xdr:rowOff>
+      <xdr:rowOff>5862</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2338,8 +2376,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="2774462" y="4191000"/>
-          <a:ext cx="9769" cy="825500"/>
+          <a:off x="2497015" y="4205653"/>
+          <a:ext cx="4885" cy="788378"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2371,15 +2409,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1245577</xdr:colOff>
+      <xdr:colOff>1066800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>29307</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>219808</xdr:colOff>
+      <xdr:colOff>155331</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>43961</xdr:rowOff>
+      <xdr:rowOff>90853</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2394,8 +2432,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="1245577" y="4147038"/>
-          <a:ext cx="1548423" cy="14654"/>
+          <a:off x="1066800" y="4185137"/>
+          <a:ext cx="1433146" cy="14654"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2424,140 +2462,6 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1216270</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>19538</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>361461</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>24423</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="文本框 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B38F983F-B758-A059-5D05-DB8A7E8558EA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1216270" y="3961423"/>
-          <a:ext cx="400537" cy="180731"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="0" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="800"/>
-            <a:t>7.02</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>5863</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>10746</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>493346</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>24423</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="文本框 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C2A2099-11D8-4AA4-A759-18DA68899C8E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2580055" y="5007708"/>
-          <a:ext cx="487483" cy="189523"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="0" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="800"/>
-            <a:t>49.14</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2565,12 +2469,12 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.41294</cdr:x>
-      <cdr:y>0.45742</cdr:y>
+      <cdr:x>0.40889</cdr:x>
+      <cdr:y>0.4675</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.48955</cdr:x>
-      <cdr:y>0.55821</cdr:y>
+      <cdr:x>0.4855</cdr:x>
+      <cdr:y>0.56829</cdr:y>
     </cdr:to>
     <cdr:cxnSp macro="">
       <cdr:nvCxnSpPr>
@@ -2585,8 +2489,8 @@
       </cdr:nvCxnSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="2027115" y="1330081"/>
-          <a:ext cx="376115" cy="293077"/>
+          <a:off x="1775575" y="1359399"/>
+          <a:ext cx="332673" cy="293079"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="straightConnector1">
           <a:avLst/>
@@ -2935,446 +2839,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2B0E6D-849C-4BD5-BD8E-0688AB77B142}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" s="8"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3">
+        <f>AVERAGE(B6:K6)</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3.65</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3.65</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3.65</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3.65</v>
+      </c>
+      <c r="I7" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3.65</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" ref="L7:L12" si="0">AVERAGE(B7:K7)</f>
+        <v>3.665</v>
+      </c>
+      <c r="M7" s="3">
+        <f>L7-$L$6</f>
+        <v>2.665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6.85</v>
+      </c>
+      <c r="D8" s="2">
+        <v>6.65</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.75</v>
+      </c>
+      <c r="F8" s="2">
+        <v>6.75</v>
+      </c>
+      <c r="G8" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J8" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="K8" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="0"/>
+        <v>6.7099999999999991</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" ref="M8:M12" si="1">L8-$L$6</f>
+        <v>5.7099999999999991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="D9" s="2">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>9</v>
+      </c>
+      <c r="H9" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9</v>
+      </c>
+      <c r="J9" s="2">
+        <v>9</v>
+      </c>
+      <c r="K9" s="2">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="L9" s="3">
+        <f t="shared" si="0"/>
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="1"/>
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>80</v>
+      </c>
+      <c r="B10" s="2">
+        <v>11.85</v>
+      </c>
+      <c r="C10" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="D10" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="F10" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="G10" s="2">
+        <v>11.85</v>
+      </c>
+      <c r="H10" s="2">
+        <v>11.75</v>
+      </c>
+      <c r="I10" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="J10" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="K10" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" si="0"/>
+        <v>11.824999999999999</v>
+      </c>
+      <c r="M10" s="3">
+        <f>L10-$L$6</f>
+        <v>10.824999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>100</v>
+      </c>
+      <c r="B11" s="2">
+        <v>14.65</v>
+      </c>
+      <c r="C11" s="2">
+        <v>14.75</v>
+      </c>
+      <c r="D11" s="2">
+        <v>14.75</v>
+      </c>
+      <c r="E11" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="F11" s="2">
+        <v>14.55</v>
+      </c>
+      <c r="G11" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="H11" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="I11" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>14.55</v>
+      </c>
+      <c r="K11" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="L11" s="3">
+        <f t="shared" si="0"/>
+        <v>14.694999999999999</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="1"/>
+        <v>13.694999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="B12" s="5">
+        <v>7.65</v>
+      </c>
+      <c r="C12" s="5">
+        <v>7.65</v>
+      </c>
+      <c r="D12" s="5">
+        <v>7.65</v>
+      </c>
+      <c r="E12" s="5">
+        <v>7.7</v>
+      </c>
+      <c r="F12" s="5">
+        <v>7.7</v>
+      </c>
+      <c r="G12" s="5">
+        <v>7.75</v>
+      </c>
+      <c r="H12" s="5">
+        <v>7.65</v>
+      </c>
+      <c r="I12" s="5">
+        <v>7.7</v>
+      </c>
+      <c r="J12" s="5">
+        <v>7.75</v>
+      </c>
+      <c r="K12" s="5">
+        <v>7.75</v>
+      </c>
+      <c r="L12" s="6">
+        <f t="shared" si="0"/>
+        <v>7.6950000000000003</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" si="1"/>
+        <v>6.6950000000000003</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1.9</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1.95</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1.8</v>
-      </c>
-      <c r="E6" s="7">
-        <v>1.95</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1.9</v>
-      </c>
-      <c r="G6" s="7">
-        <v>2</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1.95</v>
-      </c>
-      <c r="I6" s="7">
-        <v>2</v>
-      </c>
-      <c r="J6" s="7">
-        <v>1.6</v>
-      </c>
-      <c r="K6" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="L6" s="8">
-        <f>AVERAGE(B6:K6)</f>
-        <v>1.875</v>
-      </c>
-      <c r="M6" s="6" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>20</v>
-      </c>
-      <c r="B7" s="7">
-        <v>3.6</v>
-      </c>
-      <c r="C7" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="D7" s="7">
-        <v>3.95</v>
-      </c>
-      <c r="E7" s="7">
-        <v>4</v>
-      </c>
-      <c r="F7" s="7">
-        <v>3.9</v>
-      </c>
-      <c r="G7" s="7">
-        <v>3.95</v>
-      </c>
-      <c r="H7" s="7">
-        <v>3.85</v>
-      </c>
-      <c r="I7" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="J7" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="K7" s="7">
-        <v>3.95</v>
-      </c>
-      <c r="L7" s="8">
-        <f t="shared" ref="L7:L12" si="0">AVERAGE(B7:K7)</f>
-        <v>3.8300000000000005</v>
-      </c>
-      <c r="M7" s="8">
-        <f>L7-$L$6</f>
-        <v>1.9550000000000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>40</v>
-      </c>
-      <c r="B8" s="7">
-        <v>7</v>
-      </c>
-      <c r="C8" s="7">
-        <v>7.1</v>
-      </c>
-      <c r="D8" s="7">
-        <v>7.2</v>
-      </c>
-      <c r="E8" s="7">
-        <v>7.3</v>
-      </c>
-      <c r="F8" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="G8" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="H8" s="7">
-        <v>7.3</v>
-      </c>
-      <c r="I8" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="J8" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="K8" s="7">
-        <v>7.45</v>
-      </c>
-      <c r="L8" s="8">
-        <f t="shared" si="0"/>
-        <v>7.2949999999999999</v>
-      </c>
-      <c r="M8" s="8">
-        <f t="shared" ref="M8:M12" si="1">L8-$L$6</f>
-        <v>5.42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>60</v>
-      </c>
-      <c r="B9" s="7">
-        <v>9.9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>9.9499999999999993</v>
-      </c>
-      <c r="D9" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E9" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="F9" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="G9" s="7">
-        <v>10.25</v>
-      </c>
-      <c r="H9" s="7">
-        <v>10</v>
-      </c>
-      <c r="I9" s="7">
-        <v>10.1</v>
-      </c>
-      <c r="J9" s="7">
-        <v>10</v>
-      </c>
-      <c r="K9" s="7">
-        <v>10.1</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" si="0"/>
-        <v>10.09</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" si="1"/>
-        <v>8.2149999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
-        <v>80</v>
-      </c>
-      <c r="B10" s="7">
-        <v>13.05</v>
-      </c>
-      <c r="C10" s="7">
-        <v>13.1</v>
-      </c>
-      <c r="D10" s="7">
-        <v>13.3</v>
-      </c>
-      <c r="E10" s="7">
-        <v>13.4</v>
-      </c>
-      <c r="F10" s="7">
-        <v>12.9</v>
-      </c>
-      <c r="G10" s="7">
-        <v>12.9</v>
-      </c>
-      <c r="H10" s="7">
-        <v>12.9</v>
-      </c>
-      <c r="I10" s="7">
-        <v>13</v>
-      </c>
-      <c r="J10" s="7">
-        <v>13</v>
-      </c>
-      <c r="K10" s="7">
-        <v>13.1</v>
-      </c>
-      <c r="L10" s="8">
-        <f t="shared" si="0"/>
-        <v>13.065000000000001</v>
-      </c>
-      <c r="M10" s="8">
-        <f>L10-$L$6</f>
-        <v>11.190000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
-        <v>100</v>
-      </c>
-      <c r="B11" s="7">
-        <v>15.05</v>
-      </c>
-      <c r="C11" s="7">
-        <v>15.1</v>
-      </c>
-      <c r="D11" s="7">
-        <v>15.1</v>
-      </c>
-      <c r="E11" s="7">
-        <v>15.15</v>
-      </c>
-      <c r="F11" s="7">
-        <v>15.3</v>
-      </c>
-      <c r="G11" s="7">
-        <v>15.35</v>
-      </c>
-      <c r="H11" s="7">
-        <v>15.2</v>
-      </c>
-      <c r="I11" s="7">
-        <v>15.3</v>
-      </c>
-      <c r="J11" s="7">
-        <v>15.35</v>
-      </c>
-      <c r="K11" s="7">
-        <v>15.4</v>
-      </c>
-      <c r="L11" s="8">
-        <f t="shared" si="0"/>
-        <v>15.23</v>
-      </c>
-      <c r="M11" s="8">
-        <f t="shared" si="1"/>
-        <v>13.355</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="10">
-        <v>8.65</v>
-      </c>
-      <c r="C12" s="10">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="D12" s="10">
-        <v>8.75</v>
-      </c>
-      <c r="E12" s="10">
-        <v>9</v>
-      </c>
-      <c r="F12" s="10">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="G12" s="10">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H12" s="10">
-        <v>9</v>
-      </c>
-      <c r="I12" s="10">
-        <v>9.1</v>
-      </c>
-      <c r="J12" s="10">
-        <v>9</v>
-      </c>
-      <c r="K12" s="10">
-        <v>9.1</v>
-      </c>
-      <c r="L12" s="11">
-        <f t="shared" si="0"/>
-        <v>8.8899999999999988</v>
-      </c>
-      <c r="M12" s="11">
-        <f t="shared" si="1"/>
-        <v>7.0149999999999988</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="J15" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" t="s">
-        <v>20</v>
       </c>
       <c r="K15">
         <f>SLOPE(M7:M11,A7:A11)</f>
-        <v>0.14285000000000003</v>
+        <v>0.13587499999999997</v>
       </c>
     </row>
   </sheetData>
